--- a/input/Inventory Tool 58.xlsx
+++ b/input/Inventory Tool 58.xlsx
@@ -71240,7 +71240,7 @@
         </is>
       </c>
       <c r="D780" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E780" t="inlineStr">
         <is>
